--- a/ACCY122/Session/S03/ACCY122 L3 workbook.xlsx
+++ b/ACCY122/Session/S03/ACCY122 L3 workbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onlym\Desktop\Manek\Notes\SIM\UOW\2026 UOW\Learning Material\In Session Explanation\L3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Session/S03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78F06FA9-3BF7-4EA7-8FFA-000AAECD6C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C210CEBA-D4E9-7C4F-AA87-C893A3C65347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="802" xr2:uid="{526B6F88-2697-4E2F-91B5-BDD8E44991FB}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18760" tabRatio="802" activeTab="8" xr2:uid="{526B6F88-2697-4E2F-91B5-BDD8E44991FB}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="3" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="138">
   <si>
     <t>Bank</t>
   </si>
@@ -466,16 +466,58 @@
   <si>
     <t>To reset drawing to 0</t>
   </si>
+  <si>
+    <t xml:space="preserve">if insurance not yet expired, it is still an asset not an expense </t>
+  </si>
+  <si>
+    <t>1. apr,may,june has passed so paid insurance left 9mths. That 3 mths is expense 4500/12 x 3</t>
+  </si>
+  <si>
+    <t>insurance expense</t>
+  </si>
+  <si>
+    <t>supplies exp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cost </t>
+  </si>
+  <si>
+    <t>resale</t>
+  </si>
+  <si>
+    <t>tda</t>
+  </si>
+  <si>
+    <t>useful life</t>
+  </si>
+  <si>
+    <t>10yr</t>
+  </si>
+  <si>
+    <t>dep exp</t>
+  </si>
+  <si>
+    <t>rental revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salary exp  </t>
+  </si>
+  <si>
+    <t>salary</t>
+  </si>
+  <si>
+    <t>payable</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -545,13 +587,34 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos ExtraBold"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos ExtraBold"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -597,6 +660,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -788,9 +863,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -839,12 +914,12 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -865,8 +940,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -885,6 +960,22 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -919,22 +1010,15 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="5"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -981,8 +1065,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1028886" y="645488"/>
-          <a:ext cx="5410279" cy="5768610"/>
+          <a:off x="1088651" y="667900"/>
+          <a:ext cx="5948161" cy="6000198"/>
           <a:chOff x="0" y="78429"/>
           <a:chExt cx="6059328" cy="3928254"/>
         </a:xfrm>
@@ -1565,8 +1649,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8728809" y="39077"/>
-          <a:ext cx="4396153" cy="4054231"/>
+          <a:off x="9539655" y="39077"/>
+          <a:ext cx="4840654" cy="4239846"/>
           <a:chOff x="0" y="-6362"/>
           <a:chExt cx="6116694" cy="4013045"/>
         </a:xfrm>
@@ -2083,8 +2167,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7668847" y="39077"/>
-          <a:ext cx="4396154" cy="3937000"/>
+          <a:off x="8396655" y="39077"/>
+          <a:ext cx="4840654" cy="4093308"/>
           <a:chOff x="0" y="-6362"/>
           <a:chExt cx="6116694" cy="4013045"/>
         </a:xfrm>
@@ -2733,8 +2817,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6901963" y="39077"/>
-          <a:ext cx="4396153" cy="2500923"/>
+          <a:off x="7546732" y="39077"/>
+          <a:ext cx="4840654" cy="2373923"/>
           <a:chOff x="0" y="-6362"/>
           <a:chExt cx="6116694" cy="4013045"/>
         </a:xfrm>
@@ -3190,8 +3274,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8729454" y="39077"/>
-          <a:ext cx="4386607" cy="4019915"/>
+          <a:off x="9515951" y="39077"/>
+          <a:ext cx="4815313" cy="4203646"/>
           <a:chOff x="0" y="-6362"/>
           <a:chExt cx="6116694" cy="4013045"/>
         </a:xfrm>
@@ -4001,7 +4085,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A312F3C-6231-4CB6-9A9D-455E7481F633}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4011,7 +4095,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2412ECF-5158-4A9E-83E4-200E43275584}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4020,14 +4104,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B83B45-9284-4B4E-82AD-E7DB231EC9B1}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="10.90625" customWidth="1"/>
-    <col min="6" max="6" width="3.54296875" customWidth="1"/>
-    <col min="12" max="12" width="14.54296875" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="3.5" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B1" s="28" t="s">
         <v>40</v>
       </c>
@@ -4041,7 +4125,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
@@ -4062,7 +4146,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>49</v>
       </c>
@@ -4091,7 +4175,7 @@
       </c>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -4109,7 +4193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -4127,7 +4211,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -4145,7 +4229,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -4163,7 +4247,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -4181,7 +4265,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -4200,7 +4284,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>1</v>
       </c>
@@ -4224,7 +4308,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>2</v>
       </c>
@@ -4248,7 +4332,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>3</v>
       </c>
@@ -4272,7 +4356,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>4</v>
       </c>
@@ -4296,7 +4380,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>5</v>
       </c>
@@ -4320,7 +4404,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -4339,7 +4423,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -4352,7 +4436,7 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -4373,34 +4457,34 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA45E170-E699-4DE6-856C-101236F720BF}">
   <dimension ref="A1:M20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.08984375" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" customWidth="1"/>
+    <col min="3" max="3" width="9.5" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.1796875" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" customWidth="1"/>
-    <col min="9" max="9" width="2.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.1640625" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="9" max="9" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="55" t="s">
+    <row r="1" spans="1:13" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
       <c r="F1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="56"/>
+      <c r="H1" s="70"/>
       <c r="I1" s="9" t="s">
         <v>15</v>
       </c>
@@ -4409,7 +4493,7 @@
       </c>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="48" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="20" t="s">
         <v>17</v>
@@ -4446,7 +4530,7 @@
       </c>
       <c r="M2" s="15"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -4483,7 +4567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -4506,7 +4590,7 @@
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -4529,7 +4613,7 @@
       <c r="L5" s="18"/>
       <c r="M5" s="18"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -4554,7 +4638,7 @@
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -4579,7 +4663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -4602,7 +4686,7 @@
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -4627,7 +4711,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="21">
         <v>-6000</v>
@@ -4650,7 +4734,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="21">
         <v>-1400</v>
@@ -4673,7 +4757,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>7</v>
       </c>
@@ -4698,7 +4782,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>8</v>
       </c>
@@ -4721,7 +4805,7 @@
       <c r="L13" s="18"/>
       <c r="M13" s="18"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>9</v>
       </c>
@@ -4744,7 +4828,7 @@
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="21"/>
       <c r="C15" s="7"/>
@@ -4767,7 +4851,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="21"/>
       <c r="C16" s="7"/>
@@ -4784,7 +4868,7 @@
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="21"/>
       <c r="C17" s="7"/>
@@ -4801,7 +4885,7 @@
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>7</v>
       </c>
@@ -4850,40 +4934,40 @@
       </c>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="57">
+      <c r="B19" s="71">
         <f>SUM(B18:E18)</f>
         <v>33785</v>
       </c>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="59"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="73"/>
       <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="57">
+      <c r="G19" s="71">
         <f>SUM(G18:L18)</f>
         <v>33785</v>
       </c>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="58"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="59"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="73"/>
       <c r="M19" s="6"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="49"/>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="63"/>
       <c r="L20" s="1"/>
     </row>
   </sheetData>
@@ -4903,20 +4987,20 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10618C59-ED1D-4D91-A2B5-CF5B3D70AE7E}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.26953125" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.7265625" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6328125" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B1" s="28" t="s">
         <v>40</v>
       </c>
@@ -4930,7 +5014,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="25"/>
       <c r="B2" s="25"/>
       <c r="C2" s="25" t="s">
@@ -4950,7 +5034,7 @@
       <c r="I2" s="25"/>
       <c r="J2" s="25"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="25"/>
       <c r="B3" s="25" t="s">
         <v>34</v>
@@ -4972,7 +5056,7 @@
       </c>
       <c r="J3" s="25"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="25"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -5000,7 +5084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="s">
         <v>35</v>
       </c>
@@ -5015,7 +5099,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="25">
         <v>1</v>
       </c>
@@ -5035,7 +5119,7 @@
       <c r="I6" s="26"/>
       <c r="J6" s="25"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="25">
         <v>2</v>
       </c>
@@ -5055,7 +5139,7 @@
       <c r="I7" s="26"/>
       <c r="J7" s="25"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="25">
         <v>3</v>
       </c>
@@ -5073,7 +5157,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="25">
         <v>6</v>
       </c>
@@ -5091,7 +5175,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="25">
         <v>15</v>
       </c>
@@ -5117,7 +5201,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="25">
         <v>22</v>
       </c>
@@ -5136,7 +5220,7 @@
       <c r="H11" s="27"/>
       <c r="I11" s="27"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="25">
         <v>25</v>
       </c>
@@ -5156,7 +5240,7 @@
       <c r="I12" s="26"/>
       <c r="J12" s="25"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="25">
         <v>30</v>
       </c>
@@ -5178,10 +5262,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="D14" s="25"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="25"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -5201,27 +5285,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F416FB3C-3983-483F-9D0D-377B31F3A7BC}">
   <dimension ref="B1:O20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.2">
       <c r="G1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B2" s="28" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F3" t="s">
         <v>85</v>
       </c>
@@ -5238,7 +5322,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C4" s="28" t="s">
         <v>89</v>
       </c>
@@ -5256,22 +5340,22 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
-      <c r="E5" s="60" t="s">
+      <c r="E5" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="M5" s="61"/>
-      <c r="N5" s="62" t="s">
+      <c r="M5" s="50"/>
+      <c r="N5" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="O5" s="63" t="s">
+      <c r="O5" s="52" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C6" s="64" t="s">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C6" s="62" t="s">
         <v>97</v>
       </c>
       <c r="D6" s="28"/>
@@ -5290,29 +5374,29 @@
       <c r="L6" t="s">
         <v>100</v>
       </c>
-      <c r="M6" s="65" t="s">
+      <c r="M6" s="53" t="s">
         <v>11</v>
       </c>
       <c r="N6" t="s">
         <v>101</v>
       </c>
-      <c r="O6" s="66"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C7" s="64"/>
+      <c r="O6" s="54"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C7" s="62"/>
       <c r="D7" s="28"/>
-      <c r="E7" s="60" t="s">
+      <c r="E7" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="M7" s="65" t="s">
+      <c r="M7" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="O7" s="66" t="s">
+      <c r="O7" s="54" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C8" s="64"/>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C8" s="62"/>
       <c r="D8" s="28"/>
       <c r="E8" s="28" t="s">
         <v>103</v>
@@ -5320,22 +5404,22 @@
       <c r="F8" t="s">
         <v>91</v>
       </c>
-      <c r="M8" s="65" t="s">
+      <c r="M8" s="53" t="s">
         <v>104</v>
       </c>
-      <c r="O8" s="66"/>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C9" s="64"/>
+      <c r="O8" s="54"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C9" s="62"/>
       <c r="D9" s="28"/>
-      <c r="E9" s="60" t="s">
+      <c r="E9" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="M9" s="65"/>
-      <c r="O9" s="66"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C10" s="64"/>
+      <c r="M9" s="53"/>
+      <c r="O9" s="54"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C10" s="62"/>
       <c r="D10" s="28"/>
       <c r="E10" s="28" t="s">
         <v>105</v>
@@ -5355,52 +5439,52 @@
       <c r="L10" t="s">
         <v>108</v>
       </c>
-      <c r="M10" s="65" t="s">
+      <c r="M10" s="53" t="s">
         <v>102</v>
       </c>
       <c r="N10" t="s">
         <v>101</v>
       </c>
-      <c r="O10" s="66"/>
-    </row>
-    <row r="11" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O10" s="54"/>
+    </row>
+    <row r="11" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C11" s="28"/>
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
-      <c r="F11" s="67" t="s">
+      <c r="F11" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="G11" s="68" t="s">
+      <c r="G11" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="H11" s="69" t="s">
+      <c r="H11" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="M11" s="65" t="s">
+      <c r="M11" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="O11" s="66" t="s">
+      <c r="O11" s="54" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
-      <c r="E12" s="60" t="s">
+      <c r="E12" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="G12" s="70" t="s">
+      <c r="G12" s="58" t="s">
         <v>94</v>
       </c>
       <c r="H12" t="s">
         <v>113</v>
       </c>
-      <c r="M12" s="65" t="s">
+      <c r="M12" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="O12" s="66"/>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O12" s="54"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C13" s="28" t="s">
         <v>115</v>
       </c>
@@ -5414,10 +5498,10 @@
       <c r="H13" t="s">
         <v>117</v>
       </c>
-      <c r="M13" s="65"/>
-      <c r="O13" s="66"/>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="M13" s="53"/>
+      <c r="O13" s="54"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F14" t="s">
         <v>118</v>
       </c>
@@ -5427,61 +5511,61 @@
       <c r="L14" t="s">
         <v>119</v>
       </c>
-      <c r="M14" s="65" t="s">
+      <c r="M14" s="53" t="s">
         <v>102</v>
       </c>
       <c r="N14" t="s">
         <v>101</v>
       </c>
-      <c r="O14" s="66"/>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="M15" s="65" t="s">
+      <c r="O14" s="54"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M15" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="O15" s="66" t="s">
+      <c r="O15" s="54" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="M16" s="65" t="s">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M16" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="O16" s="66"/>
-    </row>
-    <row r="17" spans="11:15" x14ac:dyDescent="0.35">
-      <c r="M17" s="65"/>
-      <c r="O17" s="66"/>
-    </row>
-    <row r="18" spans="11:15" x14ac:dyDescent="0.35">
+      <c r="O16" s="54"/>
+    </row>
+    <row r="17" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="M17" s="53"/>
+      <c r="O17" s="54"/>
+    </row>
+    <row r="18" spans="11:15" x14ac:dyDescent="0.2">
       <c r="K18">
         <v>4</v>
       </c>
       <c r="L18" t="s">
         <v>122</v>
       </c>
-      <c r="M18" s="65" t="s">
+      <c r="M18" s="53" t="s">
         <v>1</v>
       </c>
       <c r="N18" t="s">
         <v>101</v>
       </c>
-      <c r="O18" s="66"/>
-    </row>
-    <row r="19" spans="11:15" x14ac:dyDescent="0.35">
-      <c r="M19" s="65" t="s">
+      <c r="O18" s="54"/>
+    </row>
+    <row r="19" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="M19" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="O19" s="66" t="s">
+      <c r="O19" s="54" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="11:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="M20" s="71" t="s">
+    <row r="20" spans="11:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M20" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="N20" s="72"/>
-      <c r="O20" s="73"/>
+      <c r="N20" s="60"/>
+      <c r="O20" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5497,34 +5581,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{381D50D4-13F1-4968-AE88-B6D32945C2B9}">
   <dimension ref="A1:M20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.08984375" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" customWidth="1"/>
+    <col min="3" max="3" width="9.5" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.1796875" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" customWidth="1"/>
-    <col min="9" max="9" width="2.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.1640625" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="9" max="9" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="50" t="s">
+    <row r="1" spans="1:13" ht="32.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
       <c r="F1" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="54"/>
+      <c r="H1" s="68"/>
       <c r="I1" s="45" t="s">
         <v>15</v>
       </c>
@@ -5533,7 +5617,7 @@
       </c>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="48" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="42" t="s">
         <v>17</v>
@@ -5570,7 +5654,7 @@
       </c>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -5607,7 +5691,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -5624,7 +5708,7 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -5641,7 +5725,7 @@
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -5658,7 +5742,7 @@
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -5677,7 +5761,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -5694,7 +5778,7 @@
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -5713,7 +5797,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
@@ -5730,7 +5814,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7"/>
@@ -5747,7 +5831,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>7</v>
       </c>
@@ -5766,7 +5850,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>8</v>
       </c>
@@ -5783,7 +5867,7 @@
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>9</v>
       </c>
@@ -5800,7 +5884,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -5815,7 +5899,7 @@
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
@@ -5832,7 +5916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
@@ -5849,7 +5933,7 @@
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>7</v>
       </c>
@@ -5898,40 +5982,40 @@
       </c>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="51">
+      <c r="B19" s="65">
         <f>SUM(B18:E18)</f>
         <v>46125</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="53"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="67"/>
       <c r="F19" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="51">
+      <c r="G19" s="65">
         <f>SUM(G18:L18)</f>
         <v>46125</v>
       </c>
-      <c r="H19" s="52"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
-      <c r="K19" s="52"/>
-      <c r="L19" s="53"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="66"/>
+      <c r="K19" s="66"/>
+      <c r="L19" s="67"/>
       <c r="M19" s="6"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="49"/>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="63"/>
       <c r="L20" s="1"/>
     </row>
   </sheetData>
@@ -5951,33 +6035,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C307D1BC-79BF-4154-B795-E817115594EB}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.08984375" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.08984375" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" customWidth="1"/>
-    <col min="8" max="8" width="2.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1640625" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="55" t="s">
+    <row r="1" spans="1:12" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
       <c r="E1" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="56" t="s">
+      <c r="F1" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="9" t="s">
         <v>15</v>
       </c>
@@ -5986,7 +6070,7 @@
       </c>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" ht="48" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
         <v>17</v>
@@ -6020,7 +6104,7 @@
       </c>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -6037,7 +6121,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -6057,7 +6141,7 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -6077,7 +6161,7 @@
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -6097,7 +6181,7 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -6119,7 +6203,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -6139,7 +6223,7 @@
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
     </row>
-    <row r="9" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -6161,7 +6245,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>7</v>
       </c>
@@ -6183,7 +6267,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>8</v>
       </c>
@@ -6203,7 +6287,7 @@
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
     </row>
-    <row r="12" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
@@ -6221,7 +6305,7 @@
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
     </row>
-    <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
@@ -6239,7 +6323,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
@@ -6259,7 +6343,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -6277,7 +6361,7 @@
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
     </row>
-    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>7</v>
       </c>
@@ -6321,38 +6405,38 @@
       </c>
       <c r="L16" s="7"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="51">
+      <c r="B17" s="65">
         <f>SUM(B16:D16)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="53"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="67"/>
       <c r="E17" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="65">
         <f>SUM(F16:K16)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="53"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="66"/>
+      <c r="K17" s="67"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="63"/>
       <c r="K18" s="1"/>
     </row>
   </sheetData>
@@ -6371,20 +6455,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6904CB14-58B2-4176-B406-2DD0650926F7}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.26953125" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.7265625" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6328125" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B1" s="28" t="s">
         <v>40</v>
       </c>
@@ -6398,7 +6482,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="25"/>
       <c r="B2" s="25"/>
       <c r="C2" s="25" t="s">
@@ -6418,7 +6502,7 @@
       <c r="I2" s="25"/>
       <c r="J2" s="25"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="25"/>
       <c r="B3" s="25" t="s">
         <v>34</v>
@@ -6440,7 +6524,7 @@
       </c>
       <c r="J3" s="25"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="25"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -6470,7 +6554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="s">
         <v>35</v>
       </c>
@@ -6483,7 +6567,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="25">
         <v>1</v>
       </c>
@@ -6497,7 +6581,7 @@
       <c r="I6" s="40"/>
       <c r="J6" s="25"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="25">
         <v>2</v>
       </c>
@@ -6511,7 +6595,7 @@
       <c r="I7" s="40"/>
       <c r="J7" s="25"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="25">
         <v>3</v>
       </c>
@@ -6527,7 +6611,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="25">
         <v>6</v>
       </c>
@@ -6543,7 +6627,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="25">
         <v>15</v>
       </c>
@@ -6559,7 +6643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="25">
         <v>22</v>
       </c>
@@ -6572,7 +6656,7 @@
       <c r="H11" s="41"/>
       <c r="I11" s="41"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="25">
         <v>25</v>
       </c>
@@ -6586,7 +6670,7 @@
       <c r="I12" s="40"/>
       <c r="J12" s="25"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="25">
         <v>30</v>
       </c>
@@ -6602,10 +6686,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="D14" s="25"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="25"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -6625,22 +6709,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F224E296-4F3D-4E57-9EBB-EEDEFC85043C}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.26953125" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="10.26953125" customWidth="1"/>
-    <col min="6" max="6" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.08984375" customWidth="1"/>
-    <col min="8" max="8" width="3.7265625" customWidth="1"/>
-    <col min="9" max="9" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="10.33203125" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" customWidth="1"/>
+    <col min="8" max="8" width="3.6640625" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D1" s="28" t="s">
         <v>40</v>
       </c>
@@ -6654,7 +6738,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="25"/>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -6676,7 +6760,7 @@
       <c r="M2" s="25"/>
       <c r="N2" s="25"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="25"/>
       <c r="B3" s="25" t="s">
         <v>34</v>
@@ -6712,7 +6796,7 @@
       </c>
       <c r="N3" s="25"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="25"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -6750,7 +6834,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="s">
         <v>57</v>
       </c>
@@ -6764,7 +6848,7 @@
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="25">
         <v>2</v>
       </c>
@@ -6782,7 +6866,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="25">
         <v>5</v>
       </c>
@@ -6800,7 +6884,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="25">
         <v>6</v>
       </c>
@@ -6820,7 +6904,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="25">
         <v>12</v>
       </c>
@@ -6840,7 +6924,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="25">
         <v>14</v>
       </c>
@@ -6860,7 +6944,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="25">
         <v>18</v>
       </c>
@@ -6880,7 +6964,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="25">
         <v>23</v>
       </c>
@@ -6900,7 +6984,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="25">
         <v>30</v>
       </c>
@@ -6920,10 +7004,10 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="H14" s="25"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="25"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -6947,33 +7031,33 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1AE0940-BE68-4C76-9FD9-88AA74550F85}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.08984375" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.90625" customWidth="1"/>
-    <col min="6" max="6" width="2.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.08984375" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" customWidth="1"/>
-    <col min="9" max="9" width="2.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.1640625" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="9" max="9" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="55" t="s">
+    <row r="1" spans="1:11" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
       <c r="E1" s="47"/>
       <c r="F1" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="56"/>
+      <c r="H1" s="70"/>
       <c r="I1" s="9" t="s">
         <v>15</v>
       </c>
@@ -6982,7 +7066,7 @@
       </c>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="48" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
         <v>17</v>
@@ -7013,7 +7097,7 @@
       </c>
       <c r="K2" s="35"/>
     </row>
-    <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -7029,7 +7113,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="46">
         <v>37500</v>
       </c>
@@ -7052,7 +7136,7 @@
       </c>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>6</v>
       </c>
@@ -7077,7 +7161,7 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>13</v>
       </c>
@@ -7102,7 +7186,7 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>22</v>
       </c>
@@ -7125,7 +7209,7 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7"/>
@@ -7142,7 +7226,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
     </row>
-    <row r="9" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
@@ -7182,36 +7266,36 @@
       </c>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="51">
+      <c r="B10" s="65">
         <f>SUM(B9:E9)</f>
         <v>83000</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="53"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="67"/>
       <c r="E10" s="38"/>
       <c r="F10" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="51">
+      <c r="G10" s="65">
         <f>SUM(G9:J9)</f>
         <v>83000</v>
       </c>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="66"/>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C11" s="1"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7229,14 +7313,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{077BD159-12E5-40C1-B142-47DD76BC2831}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="10.90625" customWidth="1"/>
-    <col min="6" max="6" width="3.54296875" customWidth="1"/>
-    <col min="12" max="12" width="14.54296875" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="3.5" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B1" s="28" t="s">
         <v>40</v>
       </c>
@@ -7250,7 +7334,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
@@ -7271,7 +7355,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>49</v>
       </c>
@@ -7300,7 +7384,7 @@
       </c>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -7318,7 +7402,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -7336,7 +7420,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -7354,7 +7438,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -7372,7 +7456,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -7390,7 +7474,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -7409,7 +7493,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>1</v>
       </c>
@@ -7427,7 +7511,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>2</v>
       </c>
@@ -7445,7 +7529,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>3</v>
       </c>
@@ -7463,7 +7547,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>4</v>
       </c>
@@ -7481,7 +7565,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>5</v>
       </c>
@@ -7499,7 +7583,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -7518,7 +7602,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -7531,7 +7615,7 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -7551,17 +7635,18 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84DD6606-B15E-42D6-85A8-458904C4FE75}">
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="3.54296875" customWidth="1"/>
-    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="3.5" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B1" s="28" t="s">
         <v>40</v>
       </c>
@@ -7571,11 +7656,12 @@
       <c r="F1" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="28"/>
+      <c r="H1" s="30" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
@@ -7587,13 +7673,20 @@
       <c r="F3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J3" s="4"/>
+      <c r="L3" t="s">
+        <v>128</v>
+      </c>
+      <c r="M3">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>61</v>
       </c>
@@ -7608,14 +7701,23 @@
         <v>58</v>
       </c>
       <c r="G4" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J4" s="4"/>
+      <c r="L4" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="M4">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>62</v>
       </c>
@@ -7627,11 +7729,20 @@
       <c r="F5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="4"/>
+      <c r="G5" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J5" s="4"/>
+      <c r="L5" t="s">
+        <v>130</v>
+      </c>
+      <c r="M5">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
       <c r="B6" s="4">
         <v>4500</v>
@@ -7647,14 +7758,21 @@
         <v>4800</v>
       </c>
       <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="4"/>
+      <c r="I6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="L6" t="s">
+        <v>131</v>
+      </c>
+      <c r="M6" s="79" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -7662,14 +7780,21 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="4">
+      <c r="H7" s="4"/>
+      <c r="I7" s="4">
         <v>-32600</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="J7" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="L7" t="s">
+        <v>133</v>
+      </c>
+      <c r="M7">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -7677,50 +7802,74 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
-      <c r="H8" s="4">
+      <c r="H8" s="4"/>
+      <c r="I8" s="4">
         <v>13200</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>1</v>
       </c>
-      <c r="B9" s="4"/>
+      <c r="B9" s="77">
+        <v>-1125</v>
+      </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H9" s="4"/>
+      <c r="I9" s="78">
+        <v>-1125</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>2</v>
       </c>
-      <c r="C10" s="4"/>
+      <c r="C10" s="77">
+        <v>-290</v>
+      </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I10" s="13">
+        <v>-290</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>3</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="D11" s="77">
+        <v>-1100</v>
+      </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H11" s="76"/>
+      <c r="I11" s="13">
+        <v>-1100</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>4</v>
       </c>
@@ -7728,12 +7877,19 @@
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="F12" s="13">
+        <v>-1200</v>
+      </c>
+      <c r="G12" s="80"/>
       <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I12" s="77">
+        <v>1200</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>5</v>
       </c>
@@ -7742,11 +7898,18 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
+      <c r="G13" s="77">
+        <v>2400</v>
+      </c>
       <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I13" s="13">
+        <v>-2400</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -7755,8 +7918,9 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -7765,8 +7929,9 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -7775,8 +7940,9 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -7786,8 +7952,9 @@
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -7796,16 +7963,30 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
+      <c r="B19" s="74" t="s">
+        <v>125</v>
+      </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B20" s="75" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ACCY122/Session/S03/ACCY122 L3 workbook.xlsx
+++ b/ACCY122/Session/S03/ACCY122 L3 workbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Session/S03/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Session\S03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C210CEBA-D4E9-7C4F-AA87-C893A3C65347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F676483-9476-4631-A67D-77DE1476423D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18760" tabRatio="802" activeTab="8" xr2:uid="{526B6F88-2697-4E2F-91B5-BDD8E44991FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="802" activeTab="8" xr2:uid="{526B6F88-2697-4E2F-91B5-BDD8E44991FB}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="3" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="142">
   <si>
     <t>Bank</t>
   </si>
@@ -507,6 +507,54 @@
   </si>
   <si>
     <t>payable</t>
+  </si>
+  <si>
+    <t>4. Unearned rental = rent received early that you still owe service for</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Someone paid you rent </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>in advance</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">You still </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>owe them future months of rent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (LIABILITY)</t>
+    </r>
+  </si>
+  <si>
+    <t>SOMEONE PAY ME 4MTHS WORTH OF RENT ON 1 JUN AND NOW IT IS ALR JUN 30 SO 1MTH OF 4.8K = 1.2K</t>
   </si>
 </sst>
 </file>
@@ -974,6 +1022,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1010,15 +1067,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1065,8 +1113,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1088651" y="667900"/>
-          <a:ext cx="5948161" cy="6000198"/>
+          <a:off x="1010210" y="656694"/>
+          <a:ext cx="5242191" cy="5884404"/>
           <a:chOff x="0" y="78429"/>
           <a:chExt cx="6059328" cy="3928254"/>
         </a:xfrm>
@@ -1649,8 +1697,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="9539655" y="39077"/>
-          <a:ext cx="4840654" cy="4239846"/>
+          <a:off x="8367347" y="39077"/>
+          <a:ext cx="4276481" cy="4105519"/>
           <a:chOff x="0" y="-6362"/>
           <a:chExt cx="6116694" cy="4013045"/>
         </a:xfrm>
@@ -2167,8 +2215,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8396655" y="39077"/>
-          <a:ext cx="4840654" cy="4093308"/>
+          <a:off x="7363559" y="39077"/>
+          <a:ext cx="4276480" cy="3819769"/>
           <a:chOff x="0" y="-6362"/>
           <a:chExt cx="6116694" cy="4013045"/>
         </a:xfrm>
@@ -2817,8 +2865,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7546732" y="39077"/>
-          <a:ext cx="4840654" cy="2373923"/>
+          <a:off x="6623540" y="39077"/>
+          <a:ext cx="4276480" cy="2434981"/>
           <a:chOff x="0" y="-6362"/>
           <a:chExt cx="6116694" cy="4013045"/>
         </a:xfrm>
@@ -3274,8 +3322,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="9515951" y="39077"/>
-          <a:ext cx="4815313" cy="4203646"/>
+          <a:off x="8357157" y="39077"/>
+          <a:ext cx="4251226" cy="4076323"/>
           <a:chOff x="0" y="-6362"/>
           <a:chExt cx="6116694" cy="4013045"/>
         </a:xfrm>
@@ -4085,7 +4133,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A312F3C-6231-4CB6-9A9D-455E7481F633}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4095,7 +4143,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2412ECF-5158-4A9E-83E4-200E43275584}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4104,14 +4152,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B83B45-9284-4B4E-82AD-E7DB231EC9B1}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="3.5" customWidth="1"/>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="3.42578125" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B1" s="28" t="s">
         <v>40</v>
       </c>
@@ -4125,7 +4173,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
@@ -4146,7 +4194,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>49</v>
       </c>
@@ -4175,7 +4223,7 @@
       </c>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -4193,7 +4241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -4211,7 +4259,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -4229,7 +4277,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -4247,7 +4295,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -4265,7 +4313,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -4284,7 +4332,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>1</v>
       </c>
@@ -4308,7 +4356,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>2</v>
       </c>
@@ -4332,7 +4380,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>3</v>
       </c>
@@ -4356,7 +4404,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>4</v>
       </c>
@@ -4380,7 +4428,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>5</v>
       </c>
@@ -4404,7 +4452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -4423,7 +4471,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -4436,7 +4484,7 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -4457,34 +4505,34 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA45E170-E699-4DE6-856C-101236F720BF}">
   <dimension ref="A1:M20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.1640625" customWidth="1"/>
-    <col min="3" max="3" width="9.5" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.1640625" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="9" max="9" width="2.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="69" t="s">
+    <row r="1" spans="1:13" ht="32.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
       <c r="F1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="70" t="s">
+      <c r="G1" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="70"/>
+      <c r="H1" s="77"/>
       <c r="I1" s="9" t="s">
         <v>15</v>
       </c>
@@ -4493,7 +4541,7 @@
       </c>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="20" t="s">
         <v>17</v>
@@ -4530,7 +4578,7 @@
       </c>
       <c r="M2" s="15"/>
     </row>
-    <row r="3" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -4567,7 +4615,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -4590,7 +4638,7 @@
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -4613,7 +4661,7 @@
       <c r="L5" s="18"/>
       <c r="M5" s="18"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -4638,7 +4686,7 @@
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -4663,7 +4711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -4686,7 +4734,7 @@
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -4711,7 +4759,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="21">
         <v>-6000</v>
@@ -4734,7 +4782,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="21">
         <v>-1400</v>
@@ -4757,7 +4805,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>7</v>
       </c>
@@ -4782,7 +4830,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>8</v>
       </c>
@@ -4805,7 +4853,7 @@
       <c r="L13" s="18"/>
       <c r="M13" s="18"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>9</v>
       </c>
@@ -4828,7 +4876,7 @@
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="21"/>
       <c r="C15" s="7"/>
@@ -4851,7 +4899,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="21"/>
       <c r="C16" s="7"/>
@@ -4868,7 +4916,7 @@
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="21"/>
       <c r="C17" s="7"/>
@@ -4885,7 +4933,7 @@
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>7</v>
       </c>
@@ -4934,40 +4982,40 @@
       </c>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="71">
+      <c r="B19" s="78">
         <f>SUM(B18:E18)</f>
         <v>33785</v>
       </c>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="73"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="80"/>
       <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="71">
+      <c r="G19" s="78">
         <f>SUM(G18:L18)</f>
         <v>33785</v>
       </c>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="72"/>
-      <c r="L19" s="73"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="79"/>
+      <c r="K19" s="79"/>
+      <c r="L19" s="80"/>
       <c r="M19" s="6"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="63"/>
-      <c r="K20" s="63"/>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
       <c r="L20" s="1"/>
     </row>
   </sheetData>
@@ -4987,20 +5035,20 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10618C59-ED1D-4D91-A2B5-CF5B3D70AE7E}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.6640625" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" s="28" t="s">
         <v>40</v>
       </c>
@@ -5014,7 +5062,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="25"/>
       <c r="B2" s="25"/>
       <c r="C2" s="25" t="s">
@@ -5034,7 +5082,7 @@
       <c r="I2" s="25"/>
       <c r="J2" s="25"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A3" s="25"/>
       <c r="B3" s="25" t="s">
         <v>34</v>
@@ -5056,7 +5104,7 @@
       </c>
       <c r="J3" s="25"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -5084,7 +5132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
         <v>35</v>
       </c>
@@ -5099,7 +5147,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <v>1</v>
       </c>
@@ -5119,7 +5167,7 @@
       <c r="I6" s="26"/>
       <c r="J6" s="25"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
         <v>2</v>
       </c>
@@ -5139,7 +5187,7 @@
       <c r="I7" s="26"/>
       <c r="J7" s="25"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <v>3</v>
       </c>
@@ -5157,7 +5205,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
         <v>6</v>
       </c>
@@ -5175,7 +5223,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <v>15</v>
       </c>
@@ -5201,7 +5249,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <v>22</v>
       </c>
@@ -5220,7 +5268,7 @@
       <c r="H11" s="27"/>
       <c r="I11" s="27"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
         <v>25</v>
       </c>
@@ -5240,7 +5288,7 @@
       <c r="I12" s="26"/>
       <c r="J12" s="25"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A13" s="25">
         <v>30</v>
       </c>
@@ -5262,10 +5310,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="D14" s="25"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A15" s="25"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -5285,27 +5333,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F416FB3C-3983-483F-9D0D-377B31F3A7BC}">
   <dimension ref="B1:O20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F3" t="s">
         <v>85</v>
       </c>
@@ -5322,7 +5370,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="28" t="s">
         <v>89</v>
       </c>
@@ -5340,7 +5388,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
       <c r="E5" s="49" t="s">
@@ -5354,8 +5402,8 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C6" s="62" t="s">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C6" s="69" t="s">
         <v>97</v>
       </c>
       <c r="D6" s="28"/>
@@ -5382,8 +5430,8 @@
       </c>
       <c r="O6" s="54"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C7" s="62"/>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C7" s="69"/>
       <c r="D7" s="28"/>
       <c r="E7" s="49" t="s">
         <v>94</v>
@@ -5395,8 +5443,8 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C8" s="62"/>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C8" s="69"/>
       <c r="D8" s="28"/>
       <c r="E8" s="28" t="s">
         <v>103</v>
@@ -5409,8 +5457,8 @@
       </c>
       <c r="O8" s="54"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C9" s="62"/>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C9" s="69"/>
       <c r="D9" s="28"/>
       <c r="E9" s="49" t="s">
         <v>94</v>
@@ -5418,8 +5466,8 @@
       <c r="M9" s="53"/>
       <c r="O9" s="54"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C10" s="62"/>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C10" s="69"/>
       <c r="D10" s="28"/>
       <c r="E10" s="28" t="s">
         <v>105</v>
@@ -5447,7 +5495,7 @@
       </c>
       <c r="O10" s="54"/>
     </row>
-    <row r="11" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="28"/>
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
@@ -5467,7 +5515,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
       <c r="E12" s="49" t="s">
@@ -5484,7 +5532,7 @@
       </c>
       <c r="O12" s="54"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C13" s="28" t="s">
         <v>115</v>
       </c>
@@ -5501,7 +5549,7 @@
       <c r="M13" s="53"/>
       <c r="O13" s="54"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
         <v>118</v>
       </c>
@@ -5519,7 +5567,7 @@
       </c>
       <c r="O14" s="54"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="M15" s="53" t="s">
         <v>120</v>
       </c>
@@ -5527,17 +5575,17 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="M16" s="53" t="s">
         <v>121</v>
       </c>
       <c r="O16" s="54"/>
     </row>
-    <row r="17" spans="11:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="11:15" x14ac:dyDescent="0.25">
       <c r="M17" s="53"/>
       <c r="O17" s="54"/>
     </row>
-    <row r="18" spans="11:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K18">
         <v>4</v>
       </c>
@@ -5552,7 +5600,7 @@
       </c>
       <c r="O18" s="54"/>
     </row>
-    <row r="19" spans="11:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="11:15" x14ac:dyDescent="0.25">
       <c r="M19" s="53" t="s">
         <v>80</v>
       </c>
@@ -5560,7 +5608,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="11:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="11:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M20" s="59" t="s">
         <v>123</v>
       </c>
@@ -5581,34 +5629,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{381D50D4-13F1-4968-AE88-B6D32945C2B9}">
   <dimension ref="A1:M20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.1640625" customWidth="1"/>
-    <col min="3" max="3" width="9.5" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.1640625" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="9" max="9" width="2.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="32.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="64" t="s">
+    <row r="1" spans="1:13" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
       <c r="F1" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="G1" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="68"/>
+      <c r="H1" s="75"/>
       <c r="I1" s="45" t="s">
         <v>15</v>
       </c>
@@ -5617,7 +5665,7 @@
       </c>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="42" t="s">
         <v>17</v>
@@ -5654,7 +5702,7 @@
       </c>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -5691,7 +5739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -5708,7 +5756,7 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -5725,7 +5773,7 @@
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -5742,7 +5790,7 @@
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -5761,7 +5809,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -5778,7 +5826,7 @@
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -5797,7 +5845,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
@@ -5814,7 +5862,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7"/>
@@ -5831,7 +5879,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>7</v>
       </c>
@@ -5850,7 +5898,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>8</v>
       </c>
@@ -5867,7 +5915,7 @@
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>9</v>
       </c>
@@ -5884,7 +5932,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -5899,7 +5947,7 @@
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
@@ -5916,7 +5964,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
@@ -5933,7 +5981,7 @@
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>7</v>
       </c>
@@ -5982,40 +6030,40 @@
       </c>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="65">
+      <c r="B19" s="72">
         <f>SUM(B18:E18)</f>
         <v>46125</v>
       </c>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="67"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="74"/>
       <c r="F19" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="65">
+      <c r="G19" s="72">
         <f>SUM(G18:L18)</f>
         <v>46125</v>
       </c>
-      <c r="H19" s="66"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="67"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="73"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="74"/>
       <c r="M19" s="6"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="63"/>
-      <c r="K20" s="63"/>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
       <c r="L20" s="1"/>
     </row>
   </sheetData>
@@ -6035,33 +6083,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C307D1BC-79BF-4154-B795-E817115594EB}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1640625" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="2.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="8" max="8" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="69" t="s">
+    <row r="1" spans="1:12" ht="32.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
       <c r="E1" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="70" t="s">
+      <c r="F1" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="77"/>
       <c r="H1" s="9" t="s">
         <v>15</v>
       </c>
@@ -6070,7 +6118,7 @@
       </c>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
         <v>17</v>
@@ -6104,7 +6152,7 @@
       </c>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -6121,7 +6169,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -6141,7 +6189,7 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -6161,7 +6209,7 @@
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -6181,7 +6229,7 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -6203,7 +6251,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -6223,7 +6271,7 @@
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
     </row>
-    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -6245,7 +6293,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>7</v>
       </c>
@@ -6267,7 +6315,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>8</v>
       </c>
@@ -6287,7 +6335,7 @@
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
     </row>
-    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
@@ -6305,7 +6353,7 @@
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
     </row>
-    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
@@ -6323,7 +6371,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
@@ -6343,7 +6391,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -6361,7 +6409,7 @@
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
     </row>
-    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>7</v>
       </c>
@@ -6405,38 +6453,38 @@
       </c>
       <c r="L16" s="7"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="65">
+      <c r="B17" s="72">
         <f>SUM(B16:D16)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="66"/>
-      <c r="D17" s="67"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="74"/>
       <c r="E17" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="65">
+      <c r="F17" s="72">
         <f>SUM(F16:K16)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="66"/>
-      <c r="K17" s="67"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="74"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C18" s="1"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="63"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
       <c r="K18" s="1"/>
     </row>
   </sheetData>
@@ -6455,20 +6503,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6904CB14-58B2-4176-B406-2DD0650926F7}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.6640625" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" s="28" t="s">
         <v>40</v>
       </c>
@@ -6482,7 +6530,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="25"/>
       <c r="B2" s="25"/>
       <c r="C2" s="25" t="s">
@@ -6502,7 +6550,7 @@
       <c r="I2" s="25"/>
       <c r="J2" s="25"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A3" s="25"/>
       <c r="B3" s="25" t="s">
         <v>34</v>
@@ -6524,7 +6572,7 @@
       </c>
       <c r="J3" s="25"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -6554,7 +6602,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
         <v>35</v>
       </c>
@@ -6567,7 +6615,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <v>1</v>
       </c>
@@ -6581,7 +6629,7 @@
       <c r="I6" s="40"/>
       <c r="J6" s="25"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
         <v>2</v>
       </c>
@@ -6595,7 +6643,7 @@
       <c r="I7" s="40"/>
       <c r="J7" s="25"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <v>3</v>
       </c>
@@ -6611,7 +6659,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
         <v>6</v>
       </c>
@@ -6627,7 +6675,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <v>15</v>
       </c>
@@ -6643,7 +6691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <v>22</v>
       </c>
@@ -6656,7 +6704,7 @@
       <c r="H11" s="41"/>
       <c r="I11" s="41"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
         <v>25</v>
       </c>
@@ -6670,7 +6718,7 @@
       <c r="I12" s="40"/>
       <c r="J12" s="25"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A13" s="25">
         <v>30</v>
       </c>
@@ -6686,10 +6734,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="D14" s="25"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A15" s="25"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -6709,22 +6757,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F224E296-4F3D-4E57-9EBB-EEDEFC85043C}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="10.33203125" customWidth="1"/>
-    <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.1640625" customWidth="1"/>
-    <col min="8" max="8" width="3.6640625" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="10.28515625" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D1" s="28" t="s">
         <v>40</v>
       </c>
@@ -6738,7 +6786,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="25"/>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -6760,7 +6808,7 @@
       <c r="M2" s="25"/>
       <c r="N2" s="25"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A3" s="25"/>
       <c r="B3" s="25" t="s">
         <v>34</v>
@@ -6796,7 +6844,7 @@
       </c>
       <c r="N3" s="25"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -6834,7 +6882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
         <v>57</v>
       </c>
@@ -6848,7 +6896,7 @@
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <v>2</v>
       </c>
@@ -6866,7 +6914,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
         <v>5</v>
       </c>
@@ -6884,7 +6932,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <v>6</v>
       </c>
@@ -6904,7 +6952,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
         <v>12</v>
       </c>
@@ -6924,7 +6972,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <v>14</v>
       </c>
@@ -6944,7 +6992,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <v>18</v>
       </c>
@@ -6964,7 +7012,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
         <v>23</v>
       </c>
@@ -6984,7 +7032,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A13" s="25">
         <v>30</v>
       </c>
@@ -7004,10 +7052,10 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
       <c r="H14" s="25"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A15" s="25"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -7031,33 +7079,33 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1AE0940-BE68-4C76-9FD9-88AA74550F85}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="2.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.1640625" customWidth="1"/>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
-    <col min="9" max="9" width="2.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="2.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="69" t="s">
+    <row r="1" spans="1:11" ht="32.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
       <c r="E1" s="47"/>
       <c r="F1" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="70" t="s">
+      <c r="G1" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="70"/>
+      <c r="H1" s="77"/>
       <c r="I1" s="9" t="s">
         <v>15</v>
       </c>
@@ -7066,7 +7114,7 @@
       </c>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
         <v>17</v>
@@ -7097,7 +7145,7 @@
       </c>
       <c r="K2" s="35"/>
     </row>
-    <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -7113,7 +7161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="46">
         <v>37500</v>
       </c>
@@ -7136,7 +7184,7 @@
       </c>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>6</v>
       </c>
@@ -7161,7 +7209,7 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>13</v>
       </c>
@@ -7186,7 +7234,7 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>22</v>
       </c>
@@ -7209,7 +7257,7 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7"/>
@@ -7226,7 +7274,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
     </row>
-    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
@@ -7266,36 +7314,36 @@
       </c>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="65">
+      <c r="B10" s="72">
         <f>SUM(B9:E9)</f>
         <v>83000</v>
       </c>
-      <c r="C10" s="66"/>
-      <c r="D10" s="67"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="74"/>
       <c r="E10" s="38"/>
       <c r="F10" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="65">
+      <c r="G10" s="72">
         <f>SUM(G9:J9)</f>
         <v>83000</v>
       </c>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="66"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="73"/>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C11" s="1"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="63"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7313,14 +7361,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{077BD159-12E5-40C1-B142-47DD76BC2831}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="3.5" customWidth="1"/>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="3.42578125" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B1" s="28" t="s">
         <v>40</v>
       </c>
@@ -7334,7 +7382,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
@@ -7355,7 +7403,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>49</v>
       </c>
@@ -7384,7 +7432,7 @@
       </c>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -7402,7 +7450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -7420,7 +7468,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -7438,7 +7486,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -7456,7 +7504,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -7474,7 +7522,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -7493,7 +7541,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>1</v>
       </c>
@@ -7511,7 +7559,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>2</v>
       </c>
@@ -7529,7 +7577,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>3</v>
       </c>
@@ -7547,7 +7595,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>4</v>
       </c>
@@ -7565,7 +7613,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>5</v>
       </c>
@@ -7583,7 +7631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -7602,7 +7650,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -7615,7 +7663,7 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -7635,18 +7683,18 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84DD6606-B15E-42D6-85A8-458904C4FE75}">
-  <dimension ref="A1:M21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="3.5" customWidth="1"/>
-    <col min="6" max="6" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.5" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" customWidth="1"/>
+    <col min="5" max="5" width="3.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" s="28" t="s">
         <v>40</v>
       </c>
@@ -7661,7 +7709,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
@@ -7686,7 +7734,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>61</v>
       </c>
@@ -7717,7 +7765,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>62</v>
       </c>
@@ -7742,7 +7790,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4">
         <v>4500</v>
@@ -7768,11 +7816,11 @@
       <c r="L6" t="s">
         <v>131</v>
       </c>
-      <c r="M6" s="79" t="s">
+      <c r="M6" s="67" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -7794,7 +7842,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -7810,11 +7858,11 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>1</v>
       </c>
-      <c r="B9" s="77">
+      <c r="B9" s="65">
         <v>-1125</v>
       </c>
       <c r="C9" s="4"/>
@@ -7823,18 +7871,18 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="78">
+      <c r="I9" s="66">
         <v>-1125</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>2</v>
       </c>
-      <c r="C10" s="77">
+      <c r="C10" s="65">
         <v>-290</v>
       </c>
       <c r="D10" s="4"/>
@@ -7849,19 +7897,19 @@
         <v>127</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>3</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="77">
+      <c r="D11" s="65">
         <v>-1100</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="76"/>
+      <c r="H11" s="64"/>
       <c r="I11" s="13">
         <v>-1100</v>
       </c>
@@ -7869,7 +7917,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>4</v>
       </c>
@@ -7880,16 +7928,16 @@
       <c r="F12" s="13">
         <v>-1200</v>
       </c>
-      <c r="G12" s="80"/>
+      <c r="G12" s="68"/>
       <c r="H12" s="4"/>
-      <c r="I12" s="77">
+      <c r="I12" s="65">
         <v>1200</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>5</v>
       </c>
@@ -7898,7 +7946,7 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="77">
+      <c r="G13" s="65">
         <v>2400</v>
       </c>
       <c r="H13" s="4"/>
@@ -7909,7 +7957,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -7920,7 +7968,7 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -7931,7 +7979,7 @@
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -7942,7 +7990,7 @@
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -7954,7 +8002,7 @@
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -7965,9 +8013,9 @@
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="62" t="s">
         <v>125</v>
       </c>
       <c r="C19" s="4"/>
@@ -7978,14 +8026,29 @@
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B20" s="75" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="63" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B21">
-        <v>4</v>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="63" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
